--- a/data/trans_dic/IP44C$otros_2023-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP44C$otros_2023-Provincia-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -489,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Adultos que han tenido algún retraso en otros pagos</t>
+          <t>Adultos que han tenido algún retraso en otros pagos (tasa de respuesta: 97,81%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -538,7 +539,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -571,24 +572,24 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 2,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,9</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,98</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -621,24 +622,24 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,62; 66,36</t>
+          <t>3,96; 62,53</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,62; 3,87</t>
+          <t>0,63; 4,4</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,89; 40,93</t>
+          <t>2,73; 45,81</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -671,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,42</t>
+          <t>0,0; 7,97</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,82</t>
+          <t>0,0; 5,64</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,53; 4,88</t>
+          <t>0,52; 4,67</t>
         </is>
       </c>
     </row>
@@ -721,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,89</t>
+          <t>0,0; 6,95</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,92</t>
+          <t>0,0; 7,87</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,56; 5,91</t>
+          <t>0,59; 5,43</t>
         </is>
       </c>
     </row>
@@ -771,24 +772,24 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0; 2,77</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0; 2,7</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0; 1,38</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -821,24 +822,24 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 2,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 2,06</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 1,12</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -871,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,87</t>
+          <t>0,0; 3,42</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,21; 8,32</t>
+          <t>1,26; 8,19</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,83; 4,68</t>
+          <t>1,01; 5,06</t>
         </is>
       </c>
     </row>
@@ -921,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>11,79; 21,98</t>
+          <t>11,44; 21,86</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>9,39; 19,71</t>
+          <t>9,29; 19,74</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>11,43; 18,82</t>
+          <t>11,67; 19,18</t>
         </is>
       </c>
     </row>
@@ -971,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>4,66; 22,83</t>
+          <t>4,49; 23,2</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3,01; 5,54</t>
+          <t>3,05; 5,7</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4,28; 14,04</t>
+          <t>4,29; 15,63</t>
         </is>
       </c>
     </row>
@@ -1007,4 +1008,750 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Adultos que han tenido algún retraso en otros pagos (tasa de respuesta: 97,81%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Almería</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Cádiz</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>33588</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2216</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>35804</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>4995; 78817</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>796; 5567</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>6901; 115728</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>1345</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>760</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>2105</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4450</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3710</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>638; 5674</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>1529</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>1596</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>3124</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4676</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>0; 5793</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>828; 7651</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Huelva</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Jaén</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Málaga</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>1236</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>5251</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>6487</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>0; 4093</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>1909; 12433</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>2730; 13722</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>21384</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>21339</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>42723</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>14964; 28582</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>14167; 30101</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>33065; 54316</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n"/>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>59082</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>31161</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>90243</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n"/>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>29306; 151302</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>22711; 42436</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>59848; 218197</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A25:A27"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP44C$otros_2023-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP44C$otros_2023-Provincia-trans_dic.xlsx
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,96; 62,53</t>
+          <t>4,67; 65,44</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,63; 4,4</t>
+          <t>0,5; 3,88</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,73; 45,81</t>
+          <t>2,76; 40,63</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,97</t>
+          <t>0,0; 7,7</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,64</t>
+          <t>0,0; 5,97</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,52; 4,67</t>
+          <t>0,51; 4,67</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,95</t>
+          <t>0,0; 8,33</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,87</t>
+          <t>0,0; 9,43</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,59; 5,43</t>
+          <t>0,67; 6,02</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,42</t>
+          <t>0,0; 4,21</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,26; 8,19</t>
+          <t>1,2; 7,56</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,01; 5,06</t>
+          <t>1,04; 5,27</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>11,44; 21,86</t>
+          <t>11,7; 22,41</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>9,29; 19,74</t>
+          <t>9,34; 19,59</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>11,67; 19,18</t>
+          <t>11,71; 19,77</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>4,49; 23,2</t>
+          <t>4,53; 28,69</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3,05; 5,7</t>
+          <t>3,03; 5,52</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4,29; 15,63</t>
+          <t>4,34; 14,28</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4995; 78817</t>
+          <t>5884; 82487</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>796; 5567</t>
+          <t>636; 4916</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6901; 115728</t>
+          <t>6965; 102637</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 4450</t>
+          <t>0; 4299</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 3710</t>
+          <t>0; 3926</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>638; 5674</t>
+          <t>626; 5684</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 4676</t>
+          <t>0; 5600</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 5793</t>
+          <t>0; 6942</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>828; 7651</t>
+          <t>946; 8485</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 4093</t>
+          <t>0; 5038</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1909; 12433</t>
+          <t>1822; 11478</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2730; 13722</t>
+          <t>2832; 14308</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>14964; 28582</t>
+          <t>15302; 29306</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>14167; 30101</t>
+          <t>14237; 29874</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>33065; 54316</t>
+          <t>33179; 55997</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>29306; 151302</t>
+          <t>29523; 187081</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>22711; 42436</t>
+          <t>22570; 41086</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>59848; 218197</t>
+          <t>60653; 199332</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP44C$otros_2023-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP44C$otros_2023-Provincia-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>26,65%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>4,0%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,67; 65,44</t>
+          <t>0,52; 3,32</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,5; 3,88</t>
+          <t>3,02; 19,72</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,76; 40,63</t>
+          <t>1,89; 8,85</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,78%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,7</t>
+          <t>0,0; 5,91</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,97</t>
+          <t>0,0; 7,49</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,51; 4,67</t>
+          <t>0,56; 4,86</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>1,9%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,33</t>
+          <t>0,0; 5,06</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,43</t>
+          <t>0,0; 7,01</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,67; 6,02</t>
+          <t>0,48; 4,79</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,31%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,21</t>
+          <t>1,32; 7,88</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,2; 7,56</t>
+          <t>0,0; 4,05</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,04; 5,27</t>
+          <t>0,83; 4,45</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>15,81%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>14,85%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>11,7; 22,41</t>
+          <t>9,27; 19,74</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>9,34; 19,59</t>
+          <t>11,31; 21,66</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>11,71; 19,77</t>
+          <t>11,1; 18,7</t>
         </is>
       </c>
     </row>
@@ -949,17 +949,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>4,84%</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>4,53; 28,69</t>
+          <t>3,13; 5,82</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3,03; 5,52</t>
+          <t>3,9; 7,27</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4,34; 14,28</t>
+          <t>3,76; 6,09</t>
         </is>
       </c>
     </row>
@@ -1035,12 +1035,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>7</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1184,17 +1184,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>33588</t>
+          <t>1716</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2216</t>
+          <t>6875</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>35804</t>
+          <t>8591</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5884; 82487</t>
+          <t>593; 3808</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>636; 4916</t>
+          <t>3012; 19687</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6965; 102637</t>
+          <t>4056; 18998</t>
         </is>
       </c>
     </row>
@@ -1234,12 +1234,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1257,17 +1257,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1345</t>
+          <t>685</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>760</t>
+          <t>1320</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2105</t>
+          <t>2005</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 4299</t>
+          <t>0; 3438</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 3926</t>
+          <t>0; 4062</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>626; 5684</t>
+          <t>633; 5459</t>
         </is>
       </c>
     </row>
@@ -1330,17 +1330,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>1529</t>
+          <t>988</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1596</t>
+          <t>1586</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3124</t>
+          <t>2575</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 5600</t>
+          <t>0; 3396</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 6942</t>
+          <t>0; 4789</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>946; 8485</t>
+          <t>654; 6482</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1549,17 +1549,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>1236</t>
+          <t>4673</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>5251</t>
+          <t>1231</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>6487</t>
+          <t>5904</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 5038</t>
+          <t>1810; 10805</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1822; 11478</t>
+          <t>0; 4800</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2832; 14308</t>
+          <t>2111; 11366</t>
         </is>
       </c>
     </row>
@@ -1599,12 +1599,12 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
           <t>32</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -1622,17 +1622,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>21384</t>
+          <t>21736</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>21339</t>
+          <t>22060</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>42723</t>
+          <t>43796</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>15302; 29306</t>
+          <t>14401; 30676</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>14237; 29874</t>
+          <t>15783; 30230</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>33179; 55997</t>
+          <t>32728; 55161</t>
         </is>
       </c>
     </row>
@@ -1672,12 +1672,12 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
           <t>45</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1695,17 +1695,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>59082</t>
+          <t>29798</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>31161</t>
+          <t>33073</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>90243</t>
+          <t>62871</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>29523; 187081</t>
+          <t>21413; 39734</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>22570; 41086</t>
+          <t>24034; 44862</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>60653; 199332</t>
+          <t>48854; 79164</t>
         </is>
       </c>
     </row>
